--- a/testcases/locations/location-left-panel-basic-information.xlsx
+++ b/testcases/locations/location-left-panel-basic-information.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3987,12 +3987,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TC-LOC-LP-024</t>
+          <t xml:space="preserve">TC-LOC-LP-024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Verify Cross-Tab Save Validation - Legal Tab Invalid</t>
+          <t>Local Office Name persists through save+reload</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4010,10 +4010,8 @@
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Legal"
-Sample input 2: "Service Charge Name"
-Sample input 3: "Basic Information"
-Sample input 4: "Union"</t>
+Sample input 1: "Parker Palm Springs QA"
+Sample input 2: "Parker Palm Springs"</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4028,23 +4026,27 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Open the location Settings page; the form has no unsaved changes</t>
+          <t>Office 1604 is open in Navigator. Basic Information tab is active</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>1. Click "Legal" tab -- Legal tab opens showing grid</t>
+          <t>1. Set Local Office Name to "Parker Palm Springs QA"</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>The Legal tab opens and displays the grid.</t>
+          <t>The Local Office Name field displays "Parker Palm Springs QA".</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -4062,12 +4064,12 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2. Clear a "Service Charge Name" dropdown -- exclamation icon appears</t>
+          <t>2. Save + confirm</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>An exclamation icon appears next to the cleared Service Charge Name dropdown.</t>
+          <t>The save completes and the confirmation is acknowledged.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -4085,12 +4087,12 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>3. Return to "Basic Information" tab (left panel)</t>
+          <t>3. Reload -- value persists</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>The Basic Information tab and left panel are displayed again.</t>
+          <t>After reload, the Local Office Name field still shows "Parker Palm Springs QA".</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -4108,35 +4110,79 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>4. Toggle "Union" checkbox -- Save becomes enabled</t>
+          <t>4. Restore to "Parker Palm Springs" + save</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>The Save button becomes enabled after the Union checkbox is toggled.</t>
+          <t>The name is restored to "Parker Palm Springs" and saved successfully.</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LP-025</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Tax Mode persists through save+reload</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>left_panel</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "International"
+Sample input 2: "US"</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Office 1604 is open in Navigator. Basic Information tab is active</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>5. Click "Save" -- observe whether save succeeds or is blocked by Legal validation</t>
+          <t>1. Select Tax Mode "International"</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Clicking Save shows either a success confirmation or a blocked error state tied to the Legal-tab validation.</t>
+          <t>The Tax Mode field displays "International".</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -4154,79 +4200,35 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>6. Document exact behavior: save blocked (expected per an invalid Legal-tab condition) OR save succeeds with Legal error persisting</t>
+          <t>2. Save + confirm</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Per requirements an invalid Legal-tab condition is a Save disabled condition. Document actual observed behavior for cross-tab save interaction</t>
+          <t>The save completes and the confirmation is acknowledged.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-025</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Local Office Name persists through save+reload</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>left_panel</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Parker Palm Springs QA"
-Sample input 2: "Parker Palm Springs"</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Office 1604 is open in Navigator. Basic Information tab is active</t>
-        </is>
-      </c>
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>1. Set Local Office Name to "Parker Palm Springs QA"</t>
+          <t>3. Reload -- persists</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>The Local Office Name field displays "Parker Palm Springs QA".</t>
+          <t>After reload, the Tax Mode field still shows "International".</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -4244,35 +4246,79 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2. Save + confirm</t>
+          <t>4. Restore to "US" + save</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>The save completes and the confirmation is acknowledged.</t>
+          <t>Tax Mode is restored to "US" and saved successfully.</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LP-026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Region persists through save+reload</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>left_panel</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Boston"
+Sample input 2: "Palm Springs"</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Office 1604 is open in Navigator. Basic Information tab is active</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>3. Reload -- value persists</t>
+          <t>1. Select Region "Boston"</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>After reload, the Local Office Name field still shows "Parker Palm Springs QA".</t>
+          <t>The Region field displays "Boston".</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -4290,79 +4336,35 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>4. Restore to "Parker Palm Springs" + save</t>
+          <t>2. Save + confirm</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>The name is restored to "Parker Palm Springs" and saved successfully.</t>
+          <t>The save completes and the confirmation is acknowledged.</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-026</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Tax Mode persists through save+reload</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>left_panel</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "International"
-Sample input 2: "US"</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Office 1604 is open in Navigator. Basic Information tab is active</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>1. Select Tax Mode "International"</t>
+          <t>3. Reload -- persists</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>The Tax Mode field displays "International".</t>
+          <t>After reload, the Region field still shows "Boston".</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -4380,35 +4382,82 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2. Save + confirm</t>
+          <t>4. Restore to "Palm Springs" + save</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>The save completes and the confirmation is acknowledged.</t>
+          <t>Region is restored to "Palm Springs" and saved successfully.</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LP-027</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Pay To Address launcher opens the "Pay To List" dialog</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>left_panel</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Pay To Address"
+Sample input 2: "Pay To List"
+Sample input 3: "Search"
+Sample input 4: "Reset"
+Sample input 5: "Select"</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>On Basic Information page for location 1604</t>
+        </is>
+      </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>3. Reload -- persists</t>
+          <t>1. Click the "Pay To Address" label (the "Pay To Address" display field is disabled, so clicking its label is how the dialog is opened)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>After reload, the Tax Mode field still shows "International".</t>
+          <t>Clicking the Pay To Address label opens the "Pay To List" dialog.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -4426,79 +4475,35 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>4. Restore to "US" + save</t>
+          <t>2. Verify the "Pay To List" dialog opens</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Tax Mode is restored to "US" and saved successfully.</t>
+          <t>The "Pay To List" dialog is displayed on screen.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-027</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Region persists through save+reload</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>left_panel</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Boston"
-Sample input 2: "Palm Springs"</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Office 1604 is open in Navigator. Basic Information tab is active</t>
-        </is>
-      </c>
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>1. Select Region "Boston"</t>
+          <t>3. Verify the 5 filters (Pay To ID, Pay To Name, Address, Phone, Fax) + "Search" + "Reset" are present</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>The Region field displays "Boston".</t>
+          <t>The dialog shows 5 filters (Pay To ID, Pay To Name, Address, Phone, Fax) plus Search and Reset buttons.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -4516,12 +4521,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2. Save + confirm</t>
+          <t>4. Verify the results table renders with rows pre-loaded (the customer's Pay To list)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>The save completes and the confirmation is acknowledged.</t>
+          <t>The results table renders with the customer's Pay To list rows pre-loaded.</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -4539,105 +4544,101 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>3. Reload -- persists</t>
+          <t>5. Verify the footer "Select" (disabled) + "Cancel" buttons are present</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>After reload, the Region field still shows "Boston".</t>
+          <t>The footer shows a disabled Select button and a Cancel button.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>4. Restore to "Palm Springs" + save</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Region is restored to "Palm Springs" and saved successfully.</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-028</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Pay To Address launcher opens the "Pay To List" dialog</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LP-028</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Pay To List Select disabled until a row is checked</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
         <is>
           <t>locations</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>left_panel</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Pay To Address"
-Sample input 2: "Pay To List"
-Sample input 3: "Search"
-Sample input 4: "Reset"
-Sample input 5: "Select"</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
+Sample input 1: "Select"</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>On Basic Information page for location 1604</t>
-        </is>
-      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Pay To List dialog open</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>1. Open the Pay To List dialog</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>The "Pay To List" dialog opens.</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>1. Click the "Pay To Address" label (the "Pay To Address" display field is disabled, so clicking its label is how the dialog is opened)</t>
+          <t>2. Verify the footer "Select" button is [disabled] (no row checked)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Clicking the Pay To Address label opens the "Pay To List" dialog.</t>
+          <t>The footer Select button is disabled.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -4655,12 +4656,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2. Verify the "Pay To List" dialog opens</t>
+          <t>3. Check a row's per-row checkbox</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>The "Pay To List" dialog is displayed on screen.</t>
+          <t>The row's checkbox becomes checked.</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -4678,35 +4679,78 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>3. Verify the 5 filters (Pay To ID, Pay To Name, Address, Phone, Fax) + "Search" + "Reset" are present</t>
+          <t>4. Verify "Select" becomes enabled</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>The dialog shows 5 filters (Pay To ID, Pay To Name, Address, Phone, Fax) plus Search and Reset buttons.</t>
+          <t>The Select button becomes enabled.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LP-029</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Pay To List Cancel discards (no field change)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>left_panel</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Encore"</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Pay To List dialog open</t>
+        </is>
+      </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>4. Verify the results table renders with rows pre-loaded (the customer's Pay To list)</t>
+          <t>1. Open the dialog</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>The results table renders with the customer's Pay To list rows pre-loaded.</t>
+          <t>The "Pay To List" dialog opens.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -4724,78 +4768,35 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>5. Verify the footer "Select" (disabled) + "Cancel" buttons are present</t>
+          <t>2. Check a row (Select enables)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>The footer shows a disabled Select button and a Cancel button.</t>
+          <t>The Select button becomes enabled.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-029</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Pay To List Select disabled until a row is checked</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>left_panel</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Select"</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Pay To List dialog open</t>
-        </is>
-      </c>
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1. Open the Pay To List dialog</t>
+          <t>3. Click "Cancel"</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>The "Pay To List" dialog opens.</t>
+          <t>Clicking Cancel dismisses the "Pay To List" dialog.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -4813,12 +4814,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2. Verify the footer "Select" button is [disabled] (no row checked)</t>
+          <t>4. Verify the dialog closes</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>The footer Select button is disabled.</t>
+          <t>The "Pay To List" dialog is fully closed and no longer visible.</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -4836,124 +4837,168 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>3. Check a row's per-row checkbox</t>
+          <t>5. Verify the Pay To Address display still shows "Encore" and the left-panel "Save" stays disabled because nothing was changed</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>The row's checkbox becomes checked.</t>
+          <t>The Pay To Address display still shows "Encore" and Save stays disabled; Cancel made no changes.</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LP-030</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Pay To List Close-X and Esc each discard</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>left_panel</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Pay To List dialog open</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>4. Verify "Select" becomes enabled</t>
+          <t>1. Open the dialog</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>The Select button becomes enabled.</t>
+          <t>The "Pay To List" dialog opens.</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-030</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Pay To List Cancel discards (no field change)</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2. Re-open the dialog</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Both Esc and the Close-X dismiss the dialog without applying a selection (two independent dismiss mechanisms, asserted separately - no OR-expression)</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LP-031</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Pay To List ID filter returns the matching row</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
         <is>
           <t>locations</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>left_panel</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Encore"</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
+Sample input 1: "ID"
+Sample input 2: "Search"
+Sample input 3: "Encore Bahamas"</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
+      <c r="J135" t="inlineStr">
         <is>
           <t>Pay To List dialog open</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="K135" t="inlineStr">
         <is>
           <t>1. Open the dialog</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t>The "Pay To List" dialog opens.</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>2. Check a row (Select enables)</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>The Select button becomes enabled.</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
@@ -4971,12 +5016,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>3. Click "Cancel"</t>
+          <t>2. Type a Pay To "ID" (e.g. 7) into the Pay To ID filter</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Clicking Cancel dismisses the "Pay To List" dialog.</t>
+          <t>The Pay To ID filter field displays the entered value.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -4994,12 +5039,12 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>4. Verify the dialog closes</t>
+          <t>3. Click "Search"</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>The "Pay To List" dialog is fully closed and no longer visible.</t>
+          <t>Clicking Search runs the search and the results table updates accordingly.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
@@ -5017,12 +5062,12 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>5. Verify the Pay To Address display still shows "Encore" and the left-panel "Save" stays disabled because nothing was changed</t>
+          <t>4. Verify the results contain the matching Pay To ("Encore Bahamas" for ID 7)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>The Pay To Address display still shows "Encore" and Save stays disabled; Cancel made no changes.</t>
+          <t>The Pay To ID filter is a precise filter - searching an ID returns the matching Pay To (this is the restore-anchor mechanism the persistence case relies on). Content/existence asserted, not an exact row count</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -5030,12 +5075,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TC-LOC-LP-031</t>
+          <t xml:space="preserve">TC-LOC-LP-032</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Pay To List Close-X and Esc each discard</t>
+          <t>Pay To List Name filter "Encore" returns multiple rows</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5052,7 +5097,10 @@
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator</t>
+Application: Navigator
+Sample input 1: "Name"
+Sample input 2: "Search"
+Sample input 3: "Encore"</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5105,80 +5153,35 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2. Re-open the dialog</t>
+          <t>2. Type Encore into the Pay To "Name" filter</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Both Esc and the Close-X dismiss the dialog without applying a selection (two independent dismiss mechanisms, asserted separately - no OR-expression)</t>
+          <t>The Pay To Name filter field displays "Encore".</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-032</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Pay To List ID filter returns the matching row</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>left_panel</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "ID"
-Sample input 2: "Search"
-Sample input 3: "Encore Bahamas"</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>Pay To List dialog open</t>
-        </is>
-      </c>
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>1. Open the dialog</t>
+          <t>3. Click "Search"</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>The "Pay To List" dialog opens.</t>
+          <t>Clicking Search runs the search and the results table updates accordingly.</t>
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
@@ -5196,35 +5199,79 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2. Type a Pay To "ID" (e.g. 7) into the Pay To ID filter</t>
+          <t>4. Verify the results contain more than one "Encore"-named row</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>The Pay To ID filter field displays the entered value.</t>
+          <t>The Pay To Name filter is a "contains" search - typing "Encore" returns multiple rows, so the name alone does not identify a single row</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LP-033</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Pay To List empty result shows "No results."</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>left_panel</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Search"
+Sample input 2: "No results."</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Pay To List dialog open</t>
+        </is>
+      </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>3. Click "Search"</t>
+          <t>1. Open the dialog</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Clicking Search runs the search and the results table updates accordingly.</t>
+          <t>The "Pay To List" dialog opens.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
@@ -5242,80 +5289,35 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>4. Verify the results contain the matching Pay To ("Encore Bahamas" for ID 7)</t>
+          <t>2. Type a non-matching Pay To ID (e.g. 99999)</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>The Pay To ID filter is a precise filter - searching an ID returns the matching Pay To (this is the restore-anchor mechanism the persistence case relies on). Content/existence asserted, not an exact row count</t>
+          <t>The Pay To ID filter field displays the entered non-matching value.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-033</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Pay To List Name filter "Encore" returns multiple rows</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>left_panel</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Name"
-Sample input 2: "Search"
-Sample input 3: "Encore"</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Pay To List dialog open</t>
-        </is>
-      </c>
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>1. Open the dialog</t>
+          <t>3. Click "Search"</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>The "Pay To List" dialog opens.</t>
+          <t>Clicking Search runs the search and the results table updates accordingly.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
@@ -5333,35 +5335,78 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2. Type Encore into the Pay To "Name" filter</t>
+          <t>4. Verify the table shows the verbatim "No results." message (announced rejection, not silent)</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>The Pay To Name filter field displays "Encore".</t>
+          <t>A no-match search returns the verbatim "No results." empty-state - an announced rejection, not silence</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LP-034</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Pay To List Reset clears filters / restores full list</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>left_panel</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Reset"</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Pay To List dialog open</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>3. Click "Search"</t>
+          <t>1. Open the dialog</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Clicking Search runs the search and the results table updates accordingly.</t>
+          <t>The "Pay To List" dialog opens.</t>
         </is>
       </c>
       <c r="M147" t="inlineStr"/>
@@ -5379,79 +5424,35 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>4. Verify the results contain more than one "Encore"-named row</t>
+          <t>2. Filter by Pay To ID (e.g. 7)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>The Pay To Name filter is a "contains" search - typing "Encore" returns multiple rows, so the name alone does not identify a single row</t>
+          <t>The Pay To ID filter field displays the entered value and the results table updates accordingly.</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-034</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Pay To List empty result shows "No results."</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>left_panel</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Search"
-Sample input 2: "No results."</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Pay To List dialog open</t>
-        </is>
-      </c>
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>1. Open the dialog</t>
+          <t>3. Click "Reset"</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>The "Pay To List" dialog opens.</t>
+          <t>Clicking Reset clears the filter fields.</t>
         </is>
       </c>
       <c r="M149" t="inlineStr"/>
@@ -5469,35 +5470,79 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2. Type a non-matching Pay To ID (e.g. 99999)</t>
+          <t>4. Verify the filters clear and the full pre-loaded Pay To list is restored</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>The Pay To ID filter field displays the entered non-matching value.</t>
+          <t>All filters are cleared and the full unfiltered Pay To list is restored.</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-LP-035</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Pay To selection updates display + enables Save (no save)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>left_panel</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Encore Bahamas"
+Sample input 2: "Select"</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Pay To List dialog open. Pay To Address = "Encore"</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>3. Click "Search"</t>
+          <t>1. Open the dialog</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Clicking Search runs the search and the results table updates accordingly.</t>
+          <t>The "Pay To List" dialog opens.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
@@ -5515,78 +5560,35 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>4. Verify the table shows the verbatim "No results." message (announced rejection, not silent)</t>
+          <t>2. Filter/find Pay To ID 7 ("Encore Bahamas") and check its row</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>A no-match search returns the verbatim "No results." empty-state - an announced rejection, not silence</t>
+          <t>The Encore Bahamas row is located and its checkbox becomes checked.</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-035</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Pay To List Reset clears filters / restores full list</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>left_panel</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Reset"</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Pay To List dialog open</t>
-        </is>
-      </c>
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>1. Open the dialog</t>
+          <t>3. Click "Select"</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>The "Pay To List" dialog opens.</t>
+          <t>The dialog closes and the selection is applied.</t>
         </is>
       </c>
       <c r="M153" t="inlineStr"/>
@@ -5604,12 +5606,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2. Filter by Pay To ID (e.g. 7)</t>
+          <t>4. Verify the Pay To Address display updates to "Encore Bahamas"</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>The Pay To ID filter field displays the entered value and the results table updates accordingly.</t>
+          <t>The Pay To Address display updates to show "Encore Bahamas".</t>
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
@@ -5627,12 +5629,12 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>3. Click "Reset"</t>
+          <t>5. Verify the left-panel "Save" becomes enabled</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Clicking Reset clears the filter fields.</t>
+          <t>The left-panel Save button becomes enabled.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
@@ -5650,12 +5652,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>4. Verify the filters clear and the full pre-loaded Pay To list is restored</t>
+          <t>6. Reload WITHOUT saving</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>All filters are cleared and the full unfiltered Pay To list is restored.</t>
+          <t>After reloading without saving, the Pay To display reverts to "Encore".</t>
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
@@ -5663,12 +5665,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TC-LOC-LP-036</t>
+          <t xml:space="preserve">TC-LOC-LP-036</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Pay To selection updates display + enables Save (no save)</t>
+          <t>Pay To selection persists through save+reload (restore by ID)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5687,7 +5689,8 @@
 Location: test office 1604
 Application: Navigator
 Sample input 1: "Encore Bahamas"
-Sample input 2: "Select"</t>
+Sample input 2: "Save Changes"
+Sample input 3: "Encore"</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5712,17 +5715,17 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Pay To List dialog open. Pay To Address = "Encore"</t>
+          <t>Pay To Address = "Encore" - enforced by per-test baseline</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>1. Open the dialog</t>
+          <t>1. Open the dialog and select Pay To ID 7 ("Encore Bahamas"), then Save and confirm the "Save Changes" dialog with Ok</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>The "Pay To List" dialog opens.</t>
+          <t>The save completes and the Pay To Address field updates to "Encore Bahamas".</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
@@ -5740,12 +5743,12 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2. Filter/find Pay To ID 7 ("Encore Bahamas") and check its row</t>
+          <t>2. Reload and verify the Pay To Address persists as "Encore Bahamas"</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>The Encore Bahamas row is located and its checkbox becomes checked.</t>
+          <t>After reload, the Pay To Address field still shows "Encore Bahamas".</t>
         </is>
       </c>
       <c r="M158" t="inlineStr"/>
@@ -5763,230 +5766,47 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>3. Click "Select"</t>
+          <t>3. Restore: open the dialog, search Pay To ID 1, select that row, Save, confirm with Ok, reload, and verify the Pay To Address is back to "Encore"</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>The dialog closes and the selection is applied.</t>
+          <t>A Pay To selection persists through save and reload (unlike the Venue address selection, which does not). Office 1604 is restored to its original Pay To (ID 1) using the ID to search (the name "Encore" is ambiguous - IDs 1 and 4 share it)</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr"/>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>4. Verify the Pay To Address display updates to "Encore Bahamas"</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>The Pay To Address display updates to show "Encore Bahamas".</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr"/>
-    </row>
+    <row r="160"/>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
-      <c r="B161" t="inlineStr"/>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>5. Verify the left-panel "Save" becomes enabled</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>The left-panel Save button becomes enabled.</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr"/>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>6. Reload WITHOUT saving</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>After reloading without saving, the Pay To display reverts to "Encore".</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>TC-LOC-LP-037</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Pay To selection persists through save+reload (restore by ID)</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>left_panel</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Encore Bahamas"
-Sample input 2: "Save Changes"
-Sample input 3: "Encore"</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>Pay To Address = "Encore" - enforced by per-test baseline</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>1. Open the dialog and select Pay To ID 7 ("Encore Bahamas"), then Save and confirm the "Save Changes" dialog with Ok</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>The save completes and the Pay To Address field updates to "Encore Bahamas".</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>2. Reload and verify the Pay To Address persists as "Encore Bahamas"</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>After reload, the Pay To Address field still shows "Encore Bahamas".</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>3. Restore: open the dialog, search Pay To ID 1, select that row, Save, confirm with Ok, reload, and verify the Pay To Address is back to "Encore"</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>A Pay To selection persists through save and reload (unlike the Venue address selection, which does not). Office 1604 is restored to its original Pay To (ID 1) using the ID to search (the name "Encore" is ambiguous - IDs 1 and 4 share it)</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr"/>
-    </row>
-    <row r="166"/>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Location — Left Panel / Basic Information</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr"/>
-      <c r="D167" s="2" t="inlineStr"/>
-      <c r="E167" s="2" t="inlineStr"/>
-      <c r="F167" s="2" t="inlineStr"/>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>Automated: 36 / Pending: 1</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr"/>
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated: 36 / Pending: 0</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>Pass:36 Fail:0 Skipped:0 Blocked:0</t>
         </is>
       </c>
-      <c r="J167" s="2" t="inlineStr"/>
-      <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="2" t="inlineStr"/>
-      <c r="M167" s="2" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr">
         <is>
           <t>Last Updated: 2026-07-28</t>
         </is>
